--- a/postman_requete.xlsx
+++ b/postman_requete.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\VPProjects\insurance-beneficiary-api\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6740BFD-2BFE-4A02-8F70-8A59E05CA03E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5877A69E-E400-4396-A16F-64FED29D0468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="31">
   <si>
     <t>Nom de la requête</t>
   </si>
@@ -36,9 +36,6 @@
     <t>URL</t>
   </si>
   <si>
-    <t>Body (exemple)</t>
-  </si>
-  <si>
     <t>POST</t>
   </si>
   <si>
@@ -51,9 +48,6 @@
     <t>{ "nomCompagnie": "Assurance Malagasy", "contact": "Jean Nirina", "mail": "contact@assurance.mg" }</t>
   </si>
   <si>
-    <t>{ "nomBeneficiaire": "Voahirana", "lienParente": "Vadiko", "idEmploye": 2 }</t>
-  </si>
-  <si>
     <t>{ "idEmploye": 2, "idRH": 2, "idBeneficiaire": 2 }</t>
   </si>
   <si>
@@ -112,6 +106,18 @@
   </si>
   <si>
     <t>Voir toutes les Compagnies</t>
+  </si>
+  <si>
+    <t>Body</t>
+  </si>
+  <si>
+    <t>Voir toutes les demandes de MAJ</t>
+  </si>
+  <si>
+    <t>http://localhost:3000/api/demandes/</t>
+  </si>
+  <si>
+    <t>{ "nomBeneficiaire": "Voahirana", "lienParente": "epouse", "idEmploye": 2 }</t>
   </si>
 </sst>
 </file>
@@ -177,7 +183,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -194,6 +200,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -475,16 +482,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="40.77734375" customWidth="1"/>
     <col min="2" max="2" width="35.21875" customWidth="1"/>
     <col min="3" max="3" width="51" customWidth="1"/>
-    <col min="4" max="4" width="55.109375" customWidth="1"/>
+    <col min="4" max="4" width="62.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="43.2">
+    <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -495,138 +502,149 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>3</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="37.799999999999997" customHeight="1">
       <c r="A2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="22.2" customHeight="1">
+      <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="40.200000000000003" customHeight="1">
-      <c r="A3" s="1" t="s">
+    <row r="4" spans="1:4" ht="25.8" customHeight="1">
+      <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="3" t="s">
+      <c r="B4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D4" s="4" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="47.4" customHeight="1">
-      <c r="A4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="30.6" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="28.2" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="25.8" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D7" s="5"/>
     </row>
     <row r="8" spans="1:4" ht="26.4" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D8" s="5"/>
     </row>
     <row r="9" spans="1:4" ht="27.6" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>13</v>
       </c>
       <c r="D9" s="5"/>
     </row>
     <row r="10" spans="1:4" ht="30" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D10" s="5"/>
     </row>
     <row r="11" spans="1:4" ht="27.6" customHeight="1">
       <c r="A11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="5"/>
+    </row>
+    <row r="12" spans="1:4" ht="24.6" customHeight="1">
+      <c r="A12" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="5"/>
+      <c r="B12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>29</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -640,8 +658,9 @@
     <hyperlink ref="C9" r:id="rId8" xr:uid="{2721A973-C162-4625-BDC2-93F4CA25F58F}"/>
     <hyperlink ref="C10" r:id="rId9" xr:uid="{AD6ECE41-1209-46AD-83F9-1CA666F36100}"/>
     <hyperlink ref="C11" r:id="rId10" xr:uid="{12128E24-F45B-426A-88AE-1C7F75FF0BFC}"/>
+    <hyperlink ref="C12" r:id="rId11" xr:uid="{884404A3-5E1B-4F0D-A4F5-A9337C7E9222}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId11"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId12"/>
 </worksheet>
 </file>